--- a/data/trans_dic/IP11C$nada-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$nada-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que a consecuencia del accidente no necesitaron asistencia sanitaria</t>
+          <t>Menores que a consecuencia del accidente no necesitaron asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,32 +717,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,15; 85,8</t>
+          <t>14,49; 85,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,7; 78,25</t>
+          <t>29,88; 77,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,47; 70,92</t>
+          <t>9,42; 71,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 54,36</t>
+          <t>6,84; 49,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,43; 64,82</t>
+          <t>21,03; 70,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,23; 56,95</t>
+          <t>22,33; 57,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,83</t>
+          <t>0,0; 81,29</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,26; 52,62</t>
+          <t>13,04; 50,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,5; 70,09</t>
+          <t>31,63; 70,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 85,49</t>
+          <t>0,0; 84,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,61; 42,47</t>
+          <t>8,24; 41,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,27; 56,52</t>
+          <t>26,31; 58,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,06</t>
+          <t>0,0; 26,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,32; 39,51</t>
+          <t>13,34; 39,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34,18; 57,71</t>
+          <t>33,59; 58,99</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,1</t>
+          <t>0,0; 20,71</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,6</t>
+          <t>0,0; 44,97</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,03; 53,95</t>
+          <t>6,04; 53,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,05; 56,1</t>
+          <t>6,6; 56,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,91</t>
+          <t>0,0; 29,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,33</t>
+          <t>0,0; 35,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,78; 38,01</t>
+          <t>4,72; 42,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 32,32</t>
+          <t>3,36; 30,94</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,49; 34,95</t>
+          <t>8,63; 33,7</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 26,48</t>
+          <t>3,18; 25,7</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1136,57 +1137,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,19; 51,94</t>
+          <t>7,29; 52,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,11; 46,56</t>
+          <t>5,82; 46,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,41</t>
+          <t>0,0; 31,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,8</t>
+          <t>0,0; 44,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,3</t>
+          <t>0,0; 29,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,27; 28,3</t>
+          <t>5,31; 28,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,16; 37,5</t>
+          <t>5,18; 38,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,17</t>
+          <t>0,0; 36,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 28,78</t>
+          <t>3,29; 28,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,01; 28,8</t>
+          <t>7,38; 28,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,14; 29,12</t>
+          <t>3,4; 28,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,2; 40,43</t>
+          <t>16,7; 40,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,63; 52,6</t>
+          <t>29,18; 51,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,54</t>
+          <t>0,0; 15,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,7; 31,92</t>
+          <t>3,8; 35,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,76; 25,43</t>
+          <t>8,31; 26,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,87; 34,51</t>
+          <t>17,87; 34,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,45; 26,39</t>
+          <t>8,11; 28,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,13</t>
+          <t>0,0; 14,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,38; 28,35</t>
+          <t>14,11; 29,08</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,12; 38,15</t>
+          <t>25,25; 38,74</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,19; 19,41</t>
+          <t>5,7; 18,58</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 16,92</t>
+          <t>1,9; 17,67</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que a consecuencia del accidente no necesitaron asistencia sanitaria (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5810</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2511</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7795</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>511; 3002</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3201; 8271</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>663; 5023</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>630; 4595</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2739</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2222; 7424</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>4449; 11486</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3136</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3824</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9533</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1413</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3449</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>11970</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>7273</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>21503</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1413</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1743; 6771</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5841; 13057</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3154</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1323; 6707</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7429; 16450</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3023</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3926; 11733</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>15687; 27552</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3671</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4171</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1971</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2949</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1386</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2784</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4335</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>531; 4723</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>712; 6052</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3240</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4430</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>575; 5239</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>667; 6143</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2005; 7830</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>587; 4742</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2129</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2689</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>877</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3216</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2374</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2808</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5904</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3112</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1587</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>701; 5072</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>684; 5464</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3038</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3493</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3588</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1246; 6712</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>747; 5546</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3461</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>724; 6284</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2600; 9885</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>817; 6961</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4840</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>9737</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20980</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2291</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7452</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>18558</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6309</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>17189</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>39538</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>7048</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>5896; 14142</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>15090; 26797</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3583</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>652; 6040</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3867; 12335</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>13112; 25075</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3301; 11436</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3557</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>11547; 23800</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>31581; 48464</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3650; 11910</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>781; 7278</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11C$nada-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$nada-Edad-trans_dic.xlsx
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,49; 85,06</t>
+          <t>15,16; 85,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,88; 77,21</t>
+          <t>30,16; 77,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,42; 71,38</t>
+          <t>9,36; 70,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,84; 49,89</t>
+          <t>6,97; 44,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,03; 70,27</t>
+          <t>17,27; 65,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,33; 57,65</t>
+          <t>22,22; 57,97</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,04; 50,67</t>
+          <t>12,98; 52,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,63; 70,69</t>
+          <t>32,54; 71,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,22 +872,22 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 84,83</t>
+          <t>0,0; 76,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,24; 41,77</t>
+          <t>7,96; 42,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,31; 58,26</t>
+          <t>27,44; 56,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,56</t>
+          <t>0,0; 30,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -897,22 +897,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,34; 39,88</t>
+          <t>13,27; 37,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33,59; 58,99</t>
+          <t>34,15; 57,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,71</t>
+          <t>0,0; 20,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,97</t>
+          <t>0,0; 46,47</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,04; 53,71</t>
+          <t>6,0; 53,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,6; 56,16</t>
+          <t>8,63; 56,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1017,17 +1017,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,29</t>
+          <t>0,0; 36,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,56</t>
+          <t>0,0; 33,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,72; 42,97</t>
+          <t>4,76; 39,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 30,94</t>
+          <t>3,97; 30,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,63; 33,7</t>
+          <t>8,45; 36,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,18; 25,7</t>
+          <t>3,18; 27,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 52,73</t>
+          <t>7,01; 51,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,82; 46,48</t>
+          <t>5,81; 47,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,52</t>
+          <t>0,0; 32,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,79</t>
+          <t>0,0; 43,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,01</t>
+          <t>0,0; 29,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,31; 28,59</t>
+          <t>5,28; 27,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 38,47</t>
+          <t>5,21; 38,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,68</t>
+          <t>0,0; 39,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,29; 28,58</t>
+          <t>3,25; 29,04</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,38; 28,06</t>
+          <t>7,79; 28,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 28,94</t>
+          <t>3,43; 29,13</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,09</t>
+          <t>0,0; 31,09</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,7; 40,06</t>
+          <t>16,38; 41,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,18; 51,82</t>
+          <t>29,94; 53,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,33</t>
+          <t>0,0; 17,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,8; 35,21</t>
+          <t>3,94; 33,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,31; 26,51</t>
+          <t>8,76; 26,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,87; 34,17</t>
+          <t>18,1; 34,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,11; 28,08</t>
+          <t>7,52; 26,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,8</t>
+          <t>0,0; 12,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,11; 29,08</t>
+          <t>14,35; 28,66</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,25; 38,74</t>
+          <t>25,15; 38,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,7; 18,58</t>
+          <t>5,82; 18,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 17,67</t>
+          <t>2,01; 15,96</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>511; 3002</t>
+          <t>535; 3009</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3201; 8271</t>
+          <t>3231; 8263</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1665,12 +1665,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>663; 5023</t>
+          <t>659; 4965</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>630; 4595</t>
+          <t>642; 4141</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1685,12 +1685,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2222; 7424</t>
+          <t>1825; 6877</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4449; 11486</t>
+          <t>4426; 11550</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1743; 6771</t>
+          <t>1735; 7049</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5841; 13057</t>
+          <t>6010; 13136</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1868,22 +1868,22 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3154</t>
+          <t>0; 2857</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1323; 6707</t>
+          <t>1278; 6755</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7429; 16450</t>
+          <t>7749; 16073</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3023</t>
+          <t>0; 3507</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1893,22 +1893,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3926; 11733</t>
+          <t>3905; 11127</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15687; 27552</t>
+          <t>15951; 26713</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 3671</t>
+          <t>0; 3606</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 4171</t>
+          <t>0; 4310</t>
         </is>
       </c>
     </row>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>531; 4723</t>
+          <t>528; 4734</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>712; 6052</t>
+          <t>931; 6055</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3240</t>
+          <t>0; 4030</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4430</t>
+          <t>0; 4200</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>575; 5239</t>
+          <t>580; 4869</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2101,17 +2101,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>667; 6143</t>
+          <t>789; 6102</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2005; 7830</t>
+          <t>1963; 8414</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>587; 4742</t>
+          <t>587; 5039</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>701; 5072</t>
+          <t>674; 4923</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>684; 5464</t>
+          <t>683; 5534</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3038</t>
+          <t>0; 3103</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3493</t>
+          <t>0; 3381</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3588</t>
+          <t>0; 3694</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1246; 6712</t>
+          <t>1239; 6434</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>747; 5546</t>
+          <t>750; 5611</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3461</t>
+          <t>0; 3703</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>724; 6284</t>
+          <t>715; 6385</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2600; 9885</t>
+          <t>2744; 9919</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>817; 6961</t>
+          <t>826; 7008</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 4840</t>
+          <t>0; 5357</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5896; 14142</t>
+          <t>5782; 14713</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15090; 26797</t>
+          <t>15485; 27624</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3583</t>
+          <t>0; 4185</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>652; 6040</t>
+          <t>676; 5804</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3867; 12335</t>
+          <t>4075; 12342</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13112; 25075</t>
+          <t>13283; 24956</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3301; 11436</t>
+          <t>3063; 10637</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3557</t>
+          <t>0; 3074</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11547; 23800</t>
+          <t>11747; 23448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31581; 48464</t>
+          <t>31462; 48005</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3650; 11910</t>
+          <t>3729; 11888</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>781; 7278</t>
+          <t>829; 6574</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11C$nada-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$nada-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,37 +649,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>35,69%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21,56%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>46,86%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>51,36%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>54,24%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>35,69%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21,56%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>46,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -717,39 +717,39 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,16; 85,26</t>
+          <t>9,47; 70,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,16; 77,14</t>
+          <t>6,96; 54,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 100,0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>15,15; 85,8</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>30,7; 78,25</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>9,36; 70,55</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,97; 44,96</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -757,17 +757,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,27; 65,09</t>
+          <t>18,43; 64,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,22; 57,97</t>
+          <t>22,23; 56,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,29</t>
+          <t>0,0; 81,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>21,47%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42,39%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6,48%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>28,62%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>51,62%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>38,02%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>21,47%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>42,39%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,48%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,98; 52,75</t>
+          <t>8,61; 42,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,54; 71,12</t>
+          <t>27,27; 56,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 33,06</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 76,85</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,96; 42,06</t>
+          <t>13,26; 52,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,44; 56,92</t>
+          <t>32,5; 70,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 81,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,27; 37,82</t>
+          <t>13,32; 39,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34,15; 57,19</t>
+          <t>34,18; 57,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,34</t>
+          <t>0,0; 20,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,47</t>
+          <t>0,0; 50,92</t>
         </is>
       </c>
     </row>
@@ -929,37 +929,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,35%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11,13%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15,71%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>22,42%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>27,36%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,35%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,13%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>15,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -997,39 +997,39 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 53,83</t>
+          <t>0,0; 36,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,63; 56,18</t>
+          <t>0,0; 35,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>4,78; 38,01</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>6,03; 53,95</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>8,05; 56,1</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 36,44</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 33,71</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>4,76; 39,94</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1037,17 +1037,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,97; 30,73</t>
+          <t>3,92; 32,32</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,45; 36,22</t>
+          <t>8,49; 34,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,18; 27,3</t>
+          <t>3,2; 26,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,49%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13,7%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16,47%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7,31%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>22,13%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>22,87%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7,66%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11,25%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,7%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,47%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,01; 51,19</t>
+          <t>0,0; 22,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,81; 47,08</t>
+          <t>5,27; 28,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,19</t>
+          <t>5,16; 37,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,37</t>
+          <t>0,0; 38,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,86</t>
+          <t>7,19; 51,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,28; 27,41</t>
+          <t>6,11; 46,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,21; 38,92</t>
+          <t>0,0; 37,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,24</t>
+          <t>0,0; 47,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 29,04</t>
+          <t>3,34; 28,78</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,79; 28,16</t>
+          <t>9,01; 28,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,43; 29,13</t>
+          <t>6,14; 29,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,09</t>
+          <t>0,0; 27,99</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>16,02%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>25,29%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15,49%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>27,58%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>40,57%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>3,16%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>13,36%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>16,02%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>25,29%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>15,49%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,38; 41,67</t>
+          <t>8,76; 25,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,94; 53,42</t>
+          <t>17,87; 34,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,91</t>
+          <t>7,45; 26,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,94; 33,84</t>
+          <t>0,0; 13,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,76; 26,53</t>
+          <t>17,2; 40,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,1; 34,01</t>
+          <t>29,63; 52,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,52; 26,12</t>
+          <t>0,0; 15,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,79</t>
+          <t>4,12; 33,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,35; 28,66</t>
+          <t>14,38; 28,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,15; 38,38</t>
+          <t>25,12; 38,15</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,82; 18,55</t>
+          <t>6,19; 19,41</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 15,96</t>
+          <t>2,28; 17,29</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,37 +1509,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1577,37 +1577,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2511</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1813</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>5810</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2511</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1283</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1645,39 +1645,39 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>535; 3009</t>
+          <t>666; 4991</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3231; 8263</t>
+          <t>641; 5007</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>0; 2739</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>535; 3028</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3288; 8382</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>659; 4965</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>642; 4141</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2739</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1685,17 +1685,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1825; 6877</t>
+          <t>1947; 6849</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4426; 11550</t>
+          <t>4429; 11346</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 3136</t>
+          <t>0; 3157</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,62 +1785,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3449</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11970</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3824</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9533</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1413</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3449</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11970</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1491</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>7273</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>21503</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>737</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>7273</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>21503</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>737</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1490</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1735; 7049</t>
+          <t>1382; 6820</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6010; 13136</t>
+          <t>7701; 15961</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0; 3762</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0; 2857</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1278; 6755</t>
+          <t>1772; 7031</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7749; 16073</t>
+          <t>6002; 12946</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3507</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2940</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3905; 11127</t>
+          <t>3921; 11624</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15951; 26713</t>
+          <t>15963; 26957</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 3606</t>
+          <t>0; 3563</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 4310</t>
+          <t>0; 4241</t>
         </is>
       </c>
     </row>
@@ -1925,37 +1925,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1993,37 +1993,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1386</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1971</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2949</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1386</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1915</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2061,39 +2061,39 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>528; 4734</t>
+          <t>0; 4082</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>931; 6055</t>
+          <t>0; 4401</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>583; 4634</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>530; 4745</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>867; 6046</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4030</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4200</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>580; 4869</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -2101,17 +2101,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>789; 6102</t>
+          <t>779; 6417</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1963; 8414</t>
+          <t>1972; 8120</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>587; 5039</t>
+          <t>590; 4888</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2133,37 +2133,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3216</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2374</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2129</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2689</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>738</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>877</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3216</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2374</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>860</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1505</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>674; 4923</t>
+          <t>0; 2759</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>683; 5534</t>
+          <t>1237; 6643</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3103</t>
+          <t>744; 5406</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3381</t>
+          <t>0; 3393</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3694</t>
+          <t>692; 4995</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1239; 6434</t>
+          <t>718; 5473</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>750; 5611</t>
+          <t>0; 3606</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3703</t>
+          <t>0; 3810</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>715; 6385</t>
+          <t>734; 6329</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2744; 9919</t>
+          <t>3173; 10146</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>826; 7008</t>
+          <t>1477; 7004</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 5357</t>
+          <t>0; 4731</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>7452</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>18558</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6309</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>9737</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>20980</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>738</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2291</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>7452</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>18558</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6309</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2996</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5782; 14713</t>
+          <t>4075; 11831</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15485; 27624</t>
+          <t>13114; 25322</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4185</t>
+          <t>3033; 10746</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>676; 5804</t>
+          <t>0; 2912</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4075; 12342</t>
+          <t>6071; 14275</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13283; 24956</t>
+          <t>15323; 27200</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3063; 10637</t>
+          <t>0; 3632</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3074</t>
+          <t>707; 5701</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11747; 23448</t>
+          <t>11767; 23199</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31462; 48005</t>
+          <t>31420; 47721</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3729; 11888</t>
+          <t>3964; 12439</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>829; 6574</t>
+          <t>900; 6818</t>
         </is>
       </c>
     </row>
